--- a/optimized_version/metadata/validation_daily_metrics/agus1_validation_daily_metrics.xlsx
+++ b/optimized_version/metadata/validation_daily_metrics/agus1_validation_daily_metrics.xlsx
@@ -467,7 +467,7 @@
         <v>45676</v>
       </c>
       <c r="B2" t="n">
-        <v>0.5379324152725476</v>
+        <v>0.2651453140345938</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -476,10 +476,10 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3257315257579094</v>
+        <v>0.1605521162807975</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3257315257579094</v>
+        <v>0.1605521162807975</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
@@ -491,7 +491,7 @@
         <v>45677</v>
       </c>
       <c r="B3" t="n">
-        <v>2.979281114321816</v>
+        <v>2.430540361702775</v>
       </c>
       <c r="C3" t="n">
         <v>24</v>
@@ -500,13 +500,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1.756003764218093</v>
+        <v>1.42273464557825</v>
       </c>
       <c r="F3" t="n">
-        <v>2.26326787885978</v>
+        <v>1.815387828360864</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.7049459963915856</v>
+        <v>-0.09692654532376932</v>
       </c>
       <c r="H3" t="n">
         <v>24</v>
@@ -517,7 +517,7 @@
         <v>45678</v>
       </c>
       <c r="B4" t="n">
-        <v>5.866213771560004</v>
+        <v>5.865560239059886</v>
       </c>
       <c r="C4" t="n">
         <v>24</v>
@@ -526,13 +526,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>2.994669078742216</v>
+        <v>2.928355730715861</v>
       </c>
       <c r="F4" t="n">
-        <v>4.547205266980416</v>
+        <v>4.809888979542398</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5347708190409146</v>
+        <v>0.4794674004172672</v>
       </c>
       <c r="H4" t="n">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>45679</v>
       </c>
       <c r="B5" t="n">
-        <v>2.657356201216746</v>
+        <v>2.197674143940761</v>
       </c>
       <c r="C5" t="n">
         <v>24</v>
@@ -552,13 +552,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1.577002012853325</v>
+        <v>1.295098015277056</v>
       </c>
       <c r="F5" t="n">
-        <v>1.973974491966459</v>
+        <v>1.752634824723558</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3162713158463901</v>
+        <v>-0.03763644775676322</v>
       </c>
       <c r="H5" t="n">
         <v>24</v>
@@ -569,7 +569,7 @@
         <v>45680</v>
       </c>
       <c r="B6" t="n">
-        <v>2.497130026026399</v>
+        <v>2.459964525892394</v>
       </c>
       <c r="C6" t="n">
         <v>24</v>
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1.485160191388182</v>
+        <v>1.454574012407956</v>
       </c>
       <c r="F6" t="n">
-        <v>1.712865245284177</v>
+        <v>1.62450045970233</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.05327049354701296</v>
+        <v>0.05260039300714414</v>
       </c>
       <c r="H6" t="n">
         <v>24</v>
@@ -595,7 +595,7 @@
         <v>45681</v>
       </c>
       <c r="B7" t="n">
-        <v>3.015151419700611</v>
+        <v>2.740801888593122</v>
       </c>
       <c r="C7" t="n">
         <v>24</v>
@@ -604,13 +604,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1.801267935441117</v>
+        <v>1.626698651694603</v>
       </c>
       <c r="F7" t="n">
-        <v>2.450388306895234</v>
+        <v>2.297955766563221</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4854339317668699</v>
+        <v>-0.3063719502882696</v>
       </c>
       <c r="H7" t="n">
         <v>24</v>
@@ -621,7 +621,7 @@
         <v>45682</v>
       </c>
       <c r="B8" t="n">
-        <v>4.82066258555365</v>
+        <v>4.550766499223617</v>
       </c>
       <c r="C8" t="n">
         <v>24</v>
@@ -630,13 +630,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>2.44457968553005</v>
+        <v>2.265839895435322</v>
       </c>
       <c r="F8" t="n">
-        <v>4.526588132427128</v>
+        <v>4.606726436407526</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5784048873401855</v>
+        <v>0.5633449845175875</v>
       </c>
       <c r="H8" t="n">
         <v>24</v>
@@ -647,7 +647,7 @@
         <v>45683</v>
       </c>
       <c r="B9" t="n">
-        <v>4.919102823830549</v>
+        <v>4.229880624963123</v>
       </c>
       <c r="C9" t="n">
         <v>24</v>
@@ -656,13 +656,13 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>2.847925663953834</v>
+        <v>2.416967829681993</v>
       </c>
       <c r="F9" t="n">
-        <v>3.875178177584185</v>
+        <v>3.612245593713946</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2090649946010094</v>
+        <v>0.3127543724525795</v>
       </c>
       <c r="H9" t="n">
         <v>24</v>
@@ -673,7 +673,7 @@
         <v>45684</v>
       </c>
       <c r="B10" t="n">
-        <v>3.501254773606838</v>
+        <v>3.020136644679959</v>
       </c>
       <c r="C10" t="n">
         <v>24</v>
@@ -682,13 +682,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>2.121657158840509</v>
+        <v>1.832992502745777</v>
       </c>
       <c r="F10" t="n">
-        <v>2.710786265080476</v>
+        <v>2.451717769647957</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9725960804730891</v>
+        <v>-0.6135727925701586</v>
       </c>
       <c r="H10" t="n">
         <v>24</v>
@@ -699,7 +699,7 @@
         <v>45685</v>
       </c>
       <c r="B11" t="n">
-        <v>2.117789821286067</v>
+        <v>2.194660047520419</v>
       </c>
       <c r="C11" t="n">
         <v>24</v>
@@ -708,13 +708,13 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>1.288919698976043</v>
+        <v>1.341499841975032</v>
       </c>
       <c r="F11" t="n">
-        <v>1.660675177349841</v>
+        <v>1.581610910479519</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.142007588635128</v>
+        <v>-0.03585485500751462</v>
       </c>
       <c r="H11" t="n">
         <v>24</v>
@@ -725,7 +725,7 @@
         <v>45686</v>
       </c>
       <c r="B12" t="n">
-        <v>2.89868279523511</v>
+        <v>2.22211616218984</v>
       </c>
       <c r="C12" t="n">
         <v>24</v>
@@ -734,13 +734,13 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1.73459289432826</v>
+        <v>1.329461757237712</v>
       </c>
       <c r="F12" t="n">
-        <v>2.082167055788536</v>
+        <v>1.576903954182576</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.005498386248334</v>
+        <v>-0.150274943773429</v>
       </c>
       <c r="H12" t="n">
         <v>24</v>
@@ -751,7 +751,7 @@
         <v>45687</v>
       </c>
       <c r="B13" t="n">
-        <v>2.564556253276314</v>
+        <v>2.068458202359058</v>
       </c>
       <c r="C13" t="n">
         <v>24</v>
@@ -760,13 +760,13 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1.544706530645303</v>
+        <v>1.243626714988654</v>
       </c>
       <c r="F13" t="n">
-        <v>1.903118058189092</v>
+        <v>1.525292614803108</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.176865589081731</v>
+        <v>-0.3983197409313997</v>
       </c>
       <c r="H13" t="n">
         <v>24</v>
@@ -777,7 +777,7 @@
         <v>45688</v>
       </c>
       <c r="B14" t="n">
-        <v>5.31408546520513</v>
+        <v>5.154420104354513</v>
       </c>
       <c r="C14" t="n">
         <v>24</v>
@@ -786,13 +786,13 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>2.793657599523788</v>
+        <v>2.685438523945093</v>
       </c>
       <c r="F14" t="n">
-        <v>4.650350531690881</v>
+        <v>4.667438150031456</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4674417506224855</v>
+        <v>0.4635208112398838</v>
       </c>
       <c r="H14" t="n">
         <v>24</v>
@@ -803,7 +803,7 @@
         <v>45689</v>
       </c>
       <c r="B15" t="n">
-        <v>5.374058350496075</v>
+        <v>5.187860389787174</v>
       </c>
       <c r="C15" t="n">
         <v>24</v>
@@ -812,13 +812,13 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>2.89841997241786</v>
+        <v>2.797033956037293</v>
       </c>
       <c r="F15" t="n">
-        <v>4.774504595368757</v>
+        <v>4.714957355833723</v>
       </c>
       <c r="G15" t="n">
-        <v>0.522955733275796</v>
+        <v>0.5347808455160468</v>
       </c>
       <c r="H15" t="n">
         <v>24</v>
@@ -829,7 +829,7 @@
         <v>45690</v>
       </c>
       <c r="B16" t="n">
-        <v>3.729088454240529</v>
+        <v>3.360442291631342</v>
       </c>
       <c r="C16" t="n">
         <v>24</v>
@@ -838,13 +838,13 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>2.113509527913836</v>
+        <v>1.900031507844793</v>
       </c>
       <c r="F16" t="n">
-        <v>3.280804595441027</v>
+        <v>3.117571475491665</v>
       </c>
       <c r="G16" t="n">
-        <v>0.04159991025375609</v>
+        <v>0.1345958870976622</v>
       </c>
       <c r="H16" t="n">
         <v>24</v>
@@ -855,7 +855,7 @@
         <v>45691</v>
       </c>
       <c r="B17" t="n">
-        <v>2.78251015531239</v>
+        <v>2.554464894758206</v>
       </c>
       <c r="C17" t="n">
         <v>24</v>
@@ -864,13 +864,13 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1.690333860977862</v>
+        <v>1.559296275016673</v>
       </c>
       <c r="F17" t="n">
-        <v>2.029347163514037</v>
+        <v>1.778727748578241</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4507354045218122</v>
+        <v>-0.1145369541615833</v>
       </c>
       <c r="H17" t="n">
         <v>24</v>
@@ -881,7 +881,7 @@
         <v>45692</v>
       </c>
       <c r="B18" t="n">
-        <v>2.928027055003591</v>
+        <v>2.774100158653907</v>
       </c>
       <c r="C18" t="n">
         <v>24</v>
@@ -890,13 +890,13 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>1.745632146274049</v>
+        <v>1.645724545563917</v>
       </c>
       <c r="F18" t="n">
-        <v>2.22471453089872</v>
+        <v>1.961566155182006</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1585817051666245</v>
+        <v>0.09929203614601323</v>
       </c>
       <c r="H18" t="n">
         <v>24</v>
@@ -907,7 +907,7 @@
         <v>45693</v>
       </c>
       <c r="B19" t="n">
-        <v>2.821301288479289</v>
+        <v>2.426608600140221</v>
       </c>
       <c r="C19" t="n">
         <v>24</v>
@@ -916,13 +916,13 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>1.722390145946295</v>
+        <v>1.4893848210238</v>
       </c>
       <c r="F19" t="n">
-        <v>1.966805593891407</v>
+        <v>1.658537380460651</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5920302611172079</v>
+        <v>-0.132084846594833</v>
       </c>
       <c r="H19" t="n">
         <v>24</v>
@@ -933,7 +933,7 @@
         <v>45694</v>
       </c>
       <c r="B20" t="n">
-        <v>4.095330616834063</v>
+        <v>3.692959864468021</v>
       </c>
       <c r="C20" t="n">
         <v>24</v>
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>2.371632687007635</v>
+        <v>2.117703001042465</v>
       </c>
       <c r="F20" t="n">
-        <v>3.290715136489374</v>
+        <v>2.922387150044489</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3856602661536268</v>
+        <v>-0.09282767638201439</v>
       </c>
       <c r="H20" t="n">
         <v>24</v>
@@ -959,7 +959,7 @@
         <v>45695</v>
       </c>
       <c r="B21" t="n">
-        <v>3.651280440350196</v>
+        <v>2.972030093138595</v>
       </c>
       <c r="C21" t="n">
         <v>24</v>
@@ -968,13 +968,13 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>2.19973028234231</v>
+        <v>1.784550356641019</v>
       </c>
       <c r="F21" t="n">
-        <v>2.537393948557719</v>
+        <v>1.993958045758039</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7134556585697398</v>
+        <v>-0.05810581944176829</v>
       </c>
       <c r="H21" t="n">
         <v>24</v>
@@ -985,7 +985,7 @@
         <v>45696</v>
       </c>
       <c r="B22" t="n">
-        <v>6.392319761863191</v>
+        <v>5.701639514960433</v>
       </c>
       <c r="C22" t="n">
         <v>24</v>
@@ -994,13 +994,13 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>3.436525333717466</v>
+        <v>3.033259213382616</v>
       </c>
       <c r="F22" t="n">
-        <v>4.850448794642229</v>
+        <v>4.511896593210951</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2481849020940362</v>
+        <v>0.3494727854048207</v>
       </c>
       <c r="H22" t="n">
         <v>24</v>
@@ -1011,7 +1011,7 @@
         <v>45697</v>
       </c>
       <c r="B23" t="n">
-        <v>9.062623362336398</v>
+        <v>8.588206154643196</v>
       </c>
       <c r="C23" t="n">
         <v>24</v>
@@ -1020,13 +1020,13 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>4.650930315760835</v>
+        <v>4.313669982235568</v>
       </c>
       <c r="F23" t="n">
-        <v>7.447367867695514</v>
+        <v>7.476634821926305</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.5666280513292845</v>
+        <v>-0.5789654367493091</v>
       </c>
       <c r="H23" t="n">
         <v>24</v>
@@ -1037,7 +1037,7 @@
         <v>45698</v>
       </c>
       <c r="B24" t="n">
-        <v>2.399518811291689</v>
+        <v>1.81979954934535</v>
       </c>
       <c r="C24" t="n">
         <v>24</v>
@@ -1046,13 +1046,13 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>1.441220469460077</v>
+        <v>1.092256651051292</v>
       </c>
       <c r="F24" t="n">
-        <v>1.799288804883196</v>
+        <v>1.508304810976753</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.5366064402622734</v>
+        <v>-0.07978956479527599</v>
       </c>
       <c r="H24" t="n">
         <v>24</v>
@@ -1063,7 +1063,7 @@
         <v>45699</v>
       </c>
       <c r="B25" t="n">
-        <v>3.098807203278604</v>
+        <v>2.607769989153638</v>
       </c>
       <c r="C25" t="n">
         <v>24</v>
@@ -1072,13 +1072,13 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>1.858062814050913</v>
+        <v>1.553249209059296</v>
       </c>
       <c r="F25" t="n">
-        <v>2.223442884673157</v>
+        <v>1.822773657895624</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.8920271457002884</v>
+        <v>-0.2715718200990895</v>
       </c>
       <c r="H25" t="n">
         <v>24</v>
@@ -1089,7 +1089,7 @@
         <v>45700</v>
       </c>
       <c r="B26" t="n">
-        <v>2.857760493030904</v>
+        <v>2.323416432345348</v>
       </c>
       <c r="C26" t="n">
         <v>24</v>
@@ -1098,13 +1098,13 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>1.720658233419059</v>
+        <v>1.399022655697928</v>
       </c>
       <c r="F26" t="n">
-        <v>2.085097688818033</v>
+        <v>1.767801068802932</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.5982433173492312</v>
+        <v>-0.1488329089806024</v>
       </c>
       <c r="H26" t="n">
         <v>24</v>
@@ -1115,7 +1115,7 @@
         <v>45701</v>
       </c>
       <c r="B27" t="n">
-        <v>2.381241418253241</v>
+        <v>2.15026146040755</v>
       </c>
       <c r="C27" t="n">
         <v>24</v>
@@ -1124,13 +1124,13 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>1.440564065320603</v>
+        <v>1.298835851557633</v>
       </c>
       <c r="F27" t="n">
-        <v>1.612026819020259</v>
+        <v>1.568641109500625</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.2348986156620561</v>
+        <v>-0.1693215752930477</v>
       </c>
       <c r="H27" t="n">
         <v>24</v>
@@ -1141,7 +1141,7 @@
         <v>45702</v>
       </c>
       <c r="B28" t="n">
-        <v>6.692480192990177</v>
+        <v>7.045113067368409</v>
       </c>
       <c r="C28" t="n">
         <v>24</v>
@@ -1150,13 +1150,13 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>2.277623876700146</v>
+        <v>2.33831798472007</v>
       </c>
       <c r="F28" t="n">
-        <v>5.978126591049201</v>
+        <v>6.322834785308451</v>
       </c>
       <c r="G28" t="n">
-        <v>0.8133200747694476</v>
+        <v>0.791170873685732</v>
       </c>
       <c r="H28" t="n">
         <v>24</v>
@@ -1167,7 +1167,7 @@
         <v>45703</v>
       </c>
       <c r="B29" t="n">
-        <v>4.629169892686337</v>
+        <v>3.162551002641772</v>
       </c>
       <c r="C29" t="n">
         <v>24</v>
@@ -1176,13 +1176,13 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>1.377079274024069</v>
+        <v>0.930351340734214</v>
       </c>
       <c r="F29" t="n">
-        <v>1.53828447405499</v>
+        <v>1.101948169802134</v>
       </c>
       <c r="G29" t="n">
-        <v>-1.118157046784963</v>
+        <v>-0.08694402448506477</v>
       </c>
       <c r="H29" t="n">
         <v>24</v>
@@ -1193,7 +1193,7 @@
         <v>45704</v>
       </c>
       <c r="B30" t="n">
-        <v>6.356379873227605</v>
+        <v>5.382986573315294</v>
       </c>
       <c r="C30" t="n">
         <v>24</v>
@@ -1202,13 +1202,13 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>2.596226234065024</v>
+        <v>2.248617361842699</v>
       </c>
       <c r="F30" t="n">
-        <v>4.513089108195124</v>
+        <v>4.51899758366046</v>
       </c>
       <c r="G30" t="n">
-        <v>0.8912025247097104</v>
+        <v>0.8909174658560577</v>
       </c>
       <c r="H30" t="n">
         <v>24</v>
@@ -1219,7 +1219,7 @@
         <v>45705</v>
       </c>
       <c r="B31" t="n">
-        <v>0.3534085593899177</v>
+        <v>0.1222593645483517</v>
       </c>
       <c r="C31" t="n">
         <v>24</v>
@@ -1228,13 +1228,13 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0.2123122370209896</v>
+        <v>0.07344694442041622</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2256408814351414</v>
+        <v>0.1015120111254849</v>
       </c>
       <c r="G31" t="n">
-        <v>-6509.078812582388</v>
+        <v>-1316.605912813979</v>
       </c>
       <c r="H31" t="n">
         <v>24</v>
@@ -1245,7 +1245,7 @@
         <v>45706</v>
       </c>
       <c r="B32" t="n">
-        <v>3.378107871083893</v>
+        <v>3.092037551234939</v>
       </c>
       <c r="C32" t="n">
         <v>24</v>
@@ -1254,13 +1254,13 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>1.963580579356354</v>
+        <v>1.781950078215914</v>
       </c>
       <c r="F32" t="n">
-        <v>2.236675183874874</v>
+        <v>2.165117061495862</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.7438294948415163</v>
+        <v>-0.6340334595737549</v>
       </c>
       <c r="H32" t="n">
         <v>24</v>
@@ -1271,7 +1271,7 @@
         <v>45707</v>
       </c>
       <c r="B33" t="n">
-        <v>2.975302802004775</v>
+        <v>2.410627219953441</v>
       </c>
       <c r="C33" t="n">
         <v>24</v>
@@ -1280,13 +1280,13 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>1.735832863150539</v>
+        <v>1.386181989353507</v>
       </c>
       <c r="F33" t="n">
-        <v>1.97419483147907</v>
+        <v>1.812141063092033</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.6329595793747989</v>
+        <v>-0.3758763854733675</v>
       </c>
       <c r="H33" t="n">
         <v>24</v>
@@ -1297,7 +1297,7 @@
         <v>45708</v>
       </c>
       <c r="B34" t="n">
-        <v>3.67469105140121</v>
+        <v>3.625509502613846</v>
       </c>
       <c r="C34" t="n">
         <v>24</v>
@@ -1306,13 +1306,13 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>2.050001753113295</v>
+        <v>2.007217171344636</v>
       </c>
       <c r="F34" t="n">
-        <v>2.869026233988347</v>
+        <v>2.861914243206598</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1112483506519996</v>
+        <v>0.115649118548322</v>
       </c>
       <c r="H34" t="n">
         <v>24</v>
@@ -1323,7 +1323,7 @@
         <v>45709</v>
       </c>
       <c r="B35" t="n">
-        <v>3.396273605400616</v>
+        <v>3.417966706208692</v>
       </c>
       <c r="C35" t="n">
         <v>24</v>
@@ -1332,13 +1332,13 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>1.965373310441525</v>
+        <v>1.955898392400645</v>
       </c>
       <c r="F35" t="n">
-        <v>2.279255882888601</v>
+        <v>2.429363457594341</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.7944084179120019</v>
+        <v>-1.038544133844447</v>
       </c>
       <c r="H35" t="n">
         <v>24</v>
@@ -1349,7 +1349,7 @@
         <v>45710</v>
       </c>
       <c r="B36" t="n">
-        <v>2.734847902466858</v>
+        <v>2.709026285533818</v>
       </c>
       <c r="C36" t="n">
         <v>24</v>
@@ -1358,13 +1358,13 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>1.585997448346266</v>
+        <v>1.554559225797681</v>
       </c>
       <c r="F36" t="n">
-        <v>2.044702368016126</v>
+        <v>2.202126331608276</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.6022232192255501</v>
+        <v>-0.8584345945189391</v>
       </c>
       <c r="H36" t="n">
         <v>24</v>
@@ -1375,7 +1375,7 @@
         <v>45711</v>
       </c>
       <c r="B37" t="n">
-        <v>2.37561274523589</v>
+        <v>2.817709329262093</v>
       </c>
       <c r="C37" t="n">
         <v>24</v>
@@ -1384,13 +1384,13 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>1.380843240222954</v>
+        <v>1.616495454665303</v>
       </c>
       <c r="F37" t="n">
-        <v>1.677008738580791</v>
+        <v>1.939229739772333</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.3329125153679897</v>
+        <v>-0.7823357578132988</v>
       </c>
       <c r="H37" t="n">
         <v>24</v>
@@ -1401,7 +1401,7 @@
         <v>45712</v>
       </c>
       <c r="B38" t="n">
-        <v>4.347658247853788</v>
+        <v>4.256244259216794</v>
       </c>
       <c r="C38" t="n">
         <v>24</v>
@@ -1410,13 +1410,13 @@
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>2.229950489296018</v>
+        <v>2.118997336136558</v>
       </c>
       <c r="F38" t="n">
-        <v>3.238464021447319</v>
+        <v>3.486410955003449</v>
       </c>
       <c r="G38" t="n">
-        <v>0.7709636050818609</v>
+        <v>0.7345495283985404</v>
       </c>
       <c r="H38" t="n">
         <v>24</v>
@@ -1427,7 +1427,7 @@
         <v>45713</v>
       </c>
       <c r="B39" t="n">
-        <v>3.51580329409013</v>
+        <v>3.385865419858266</v>
       </c>
       <c r="C39" t="n">
         <v>24</v>
@@ -1436,13 +1436,13 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>1.885010819457596</v>
+        <v>1.784352977827181</v>
       </c>
       <c r="F39" t="n">
-        <v>2.88273450140648</v>
+        <v>2.776911564218472</v>
       </c>
       <c r="G39" t="n">
-        <v>0.8498551297483273</v>
+        <v>0.8606762018670876</v>
       </c>
       <c r="H39" t="n">
         <v>24</v>
@@ -1453,7 +1453,7 @@
         <v>45714</v>
       </c>
       <c r="B40" t="n">
-        <v>2.314660636698456</v>
+        <v>2.107155023032368</v>
       </c>
       <c r="C40" t="n">
         <v>24</v>
@@ -1462,13 +1462,13 @@
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>1.387391530025253</v>
+        <v>1.266828654727789</v>
       </c>
       <c r="F40" t="n">
-        <v>1.815871003778973</v>
+        <v>1.560068954701052</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.6680915333001107</v>
+        <v>-0.2312251536853736</v>
       </c>
       <c r="H40" t="n">
         <v>24</v>
@@ -1479,7 +1479,7 @@
         <v>45715</v>
       </c>
       <c r="B41" t="n">
-        <v>2.930880471347594</v>
+        <v>2.19825495864946</v>
       </c>
       <c r="C41" t="n">
         <v>24</v>
@@ -1488,13 +1488,13 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>1.75929199361826</v>
+        <v>1.318803818607569</v>
       </c>
       <c r="F41" t="n">
-        <v>2.137352903396801</v>
+        <v>1.599513671135938</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.240719322940025</v>
+        <v>-0.2549051486470071</v>
       </c>
       <c r="H41" t="n">
         <v>24</v>
@@ -1505,7 +1505,7 @@
         <v>45716</v>
       </c>
       <c r="B42" t="n">
-        <v>1.821903278989204</v>
+        <v>1.729793393668086</v>
       </c>
       <c r="C42" t="n">
         <v>24</v>
@@ -1514,13 +1514,13 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>1.098729510997422</v>
+        <v>1.042511115160863</v>
       </c>
       <c r="F42" t="n">
-        <v>1.471542353065253</v>
+        <v>1.353731138305385</v>
       </c>
       <c r="G42" t="n">
-        <v>0.04980140223690122</v>
+        <v>0.1958562516994606</v>
       </c>
       <c r="H42" t="n">
         <v>24</v>
@@ -1531,7 +1531,7 @@
         <v>45717</v>
       </c>
       <c r="B43" t="n">
-        <v>2.97963733612046</v>
+        <v>2.588876052386084</v>
       </c>
       <c r="C43" t="n">
         <v>24</v>
@@ -1540,13 +1540,13 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>1.808424567727588</v>
+        <v>1.581603245016603</v>
       </c>
       <c r="F43" t="n">
-        <v>2.182339834065709</v>
+        <v>1.887935122205107</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.6573929229014055</v>
+        <v>-0.2403802775443158</v>
       </c>
       <c r="H43" t="n">
         <v>24</v>
@@ -1557,7 +1557,7 @@
         <v>45718</v>
       </c>
       <c r="B44" t="n">
-        <v>2.693669954971682</v>
+        <v>3.205248544505575</v>
       </c>
       <c r="C44" t="n">
         <v>24</v>
@@ -1566,13 +1566,13 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>1.527975123882293</v>
+        <v>1.799628174752714</v>
       </c>
       <c r="F44" t="n">
-        <v>1.981222547105559</v>
+        <v>2.394454029902274</v>
       </c>
       <c r="G44" t="n">
-        <v>0.7043246885936509</v>
+        <v>0.568121537535583</v>
       </c>
       <c r="H44" t="n">
         <v>24</v>
@@ -1583,7 +1583,7 @@
         <v>45719</v>
       </c>
       <c r="B45" t="n">
-        <v>3.672400408021038</v>
+        <v>3.072058164696779</v>
       </c>
       <c r="C45" t="n">
         <v>24</v>
@@ -1592,13 +1592,13 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>2.206313926012318</v>
+        <v>1.858334429064595</v>
       </c>
       <c r="F45" t="n">
-        <v>2.51553284979944</v>
+        <v>2.096014675706787</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.5946390186110648</v>
+        <v>-0.1071106756930493</v>
       </c>
       <c r="H45" t="n">
         <v>24</v>
@@ -1609,7 +1609,7 @@
         <v>45720</v>
       </c>
       <c r="B46" t="n">
-        <v>4.399461816268516</v>
+        <v>4.770138857879188</v>
       </c>
       <c r="C46" t="n">
         <v>24</v>
@@ -1618,13 +1618,13 @@
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>2.32848040286377</v>
+        <v>2.530668036053889</v>
       </c>
       <c r="F46" t="n">
-        <v>2.768107277281524</v>
+        <v>2.964298766597821</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.5312099606902208</v>
+        <v>-0.755952881432179</v>
       </c>
       <c r="H46" t="n">
         <v>24</v>
@@ -1635,7 +1635,7 @@
         <v>45721</v>
       </c>
       <c r="B47" t="n">
-        <v>2.489789225772467</v>
+        <v>2.557822971148153</v>
       </c>
       <c r="C47" t="n">
         <v>24</v>
@@ -1644,13 +1644,13 @@
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>1.352752499829482</v>
+        <v>1.395151730019412</v>
       </c>
       <c r="F47" t="n">
-        <v>1.684372281266306</v>
+        <v>1.692685328340578</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.8057335296615775</v>
+        <v>-0.8236015401901839</v>
       </c>
       <c r="H47" t="n">
         <v>24</v>
@@ -1661,7 +1661,7 @@
         <v>45722</v>
       </c>
       <c r="B48" t="n">
-        <v>3.033147341464211</v>
+        <v>2.870083981603737</v>
       </c>
       <c r="C48" t="n">
         <v>24</v>
@@ -1670,13 +1670,13 @@
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>1.622755949128481</v>
+        <v>1.541082703570525</v>
       </c>
       <c r="F48" t="n">
-        <v>2.033813258671965</v>
+        <v>1.988425198620724</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.4804817553781358</v>
+        <v>-0.4151400678973891</v>
       </c>
       <c r="H48" t="n">
         <v>24</v>
@@ -1687,7 +1687,7 @@
         <v>45723</v>
       </c>
       <c r="B49" t="n">
-        <v>2.958266885074202</v>
+        <v>2.954196767516499</v>
       </c>
       <c r="C49" t="n">
         <v>24</v>
@@ -1696,13 +1696,13 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>1.603028546096136</v>
+        <v>1.607245837382349</v>
       </c>
       <c r="F49" t="n">
-        <v>2.17262834645204</v>
+        <v>2.167206951311162</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.7344162549889006</v>
+        <v>-0.7257712198659616</v>
       </c>
       <c r="H49" t="n">
         <v>24</v>
@@ -1713,7 +1713,7 @@
         <v>45724</v>
       </c>
       <c r="B50" t="n">
-        <v>3.371846529490394</v>
+        <v>3.134300368970681</v>
       </c>
       <c r="C50" t="n">
         <v>24</v>
@@ -1722,13 +1722,13 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>1.829961578965684</v>
+        <v>1.701076213022384</v>
       </c>
       <c r="F50" t="n">
-        <v>2.208063157285131</v>
+        <v>2.069357096774002</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.7498984880641271</v>
+        <v>-0.5369535936220329</v>
       </c>
       <c r="H50" t="n">
         <v>24</v>
@@ -1739,7 +1739,7 @@
         <v>45725</v>
       </c>
       <c r="B51" t="n">
-        <v>3.129261233631656</v>
+        <v>2.984738251409545</v>
       </c>
       <c r="C51" t="n">
         <v>24</v>
@@ -1748,13 +1748,13 @@
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>1.704985106344398</v>
+        <v>1.627180416101279</v>
       </c>
       <c r="F51" t="n">
-        <v>2.075035022963486</v>
+        <v>2.005455018598045</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.4184789655645631</v>
+        <v>-0.3249451154348144</v>
       </c>
       <c r="H51" t="n">
         <v>24</v>
@@ -1765,7 +1765,7 @@
         <v>45726</v>
       </c>
       <c r="B52" t="n">
-        <v>2.626256481579322</v>
+        <v>2.477406472092433</v>
       </c>
       <c r="C52" t="n">
         <v>24</v>
@@ -1774,13 +1774,13 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>1.417121544657274</v>
+        <v>1.340563185528725</v>
       </c>
       <c r="F52" t="n">
-        <v>1.690237088353107</v>
+        <v>1.583540436128894</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.5415848314823173</v>
+        <v>-0.3531018556090377</v>
       </c>
       <c r="H52" t="n">
         <v>24</v>
@@ -1791,7 +1791,7 @@
         <v>45727</v>
       </c>
       <c r="B53" t="n">
-        <v>3.141510235639864</v>
+        <v>3.037438238589651</v>
       </c>
       <c r="C53" t="n">
         <v>24</v>
@@ -1800,13 +1800,13 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>1.675935776336429</v>
+        <v>1.621454690976751</v>
       </c>
       <c r="F53" t="n">
-        <v>2.00377275138171</v>
+        <v>1.899261378365145</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.09393801394905332</v>
+        <v>0.01719975736109114</v>
       </c>
       <c r="H53" t="n">
         <v>24</v>
@@ -1817,7 +1817,7 @@
         <v>45728</v>
       </c>
       <c r="B54" t="n">
-        <v>3.842410595423804</v>
+        <v>3.7680050300002</v>
       </c>
       <c r="C54" t="n">
         <v>24</v>
@@ -1826,13 +1826,13 @@
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>1.943889824226498</v>
+        <v>1.888771907276769</v>
       </c>
       <c r="F54" t="n">
-        <v>2.276719392473743</v>
+        <v>2.342191142732228</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.2721150366693885</v>
+        <v>-0.3463316058067092</v>
       </c>
       <c r="H54" t="n">
         <v>24</v>
@@ -1843,7 +1843,7 @@
         <v>45729</v>
       </c>
       <c r="B55" t="n">
-        <v>3.316444629294071</v>
+        <v>3.281697028642955</v>
       </c>
       <c r="C55" t="n">
         <v>24</v>
@@ -1852,13 +1852,13 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>1.700770149952918</v>
+        <v>1.668676446166348</v>
       </c>
       <c r="F55" t="n">
-        <v>2.091593334677159</v>
+        <v>2.049806415878602</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.06705035547321136</v>
+        <v>-0.02484010603130193</v>
       </c>
       <c r="H55" t="n">
         <v>24</v>
@@ -1869,7 +1869,7 @@
         <v>45730</v>
       </c>
       <c r="B56" t="n">
-        <v>3.100379305531266</v>
+        <v>3.013362424314798</v>
       </c>
       <c r="C56" t="n">
         <v>24</v>
@@ -1878,13 +1878,13 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>1.623020687334239</v>
+        <v>1.574245730608833</v>
       </c>
       <c r="F56" t="n">
-        <v>2.002851559947338</v>
+        <v>1.864462773363057</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.2350067585059179</v>
+        <v>-0.07023522550438832</v>
       </c>
       <c r="H56" t="n">
         <v>24</v>
@@ -1895,7 +1895,7 @@
         <v>45731</v>
       </c>
       <c r="B57" t="n">
-        <v>3.331506538085327</v>
+        <v>3.13816786233816</v>
       </c>
       <c r="C57" t="n">
         <v>24</v>
@@ -1904,13 +1904,13 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>1.709929056969284</v>
+        <v>1.596635198232756</v>
       </c>
       <c r="F57" t="n">
-        <v>2.016315342199644</v>
+        <v>1.835303065463165</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.3421154504386492</v>
+        <v>-0.1119584170328165</v>
       </c>
       <c r="H57" t="n">
         <v>24</v>
@@ -1921,7 +1921,7 @@
         <v>45732</v>
       </c>
       <c r="B58" t="n">
-        <v>8.789490100017076</v>
+        <v>8.586171438993977</v>
       </c>
       <c r="C58" t="n">
         <v>24</v>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>3.510735182875643</v>
+        <v>3.423087963616849</v>
       </c>
       <c r="F58" t="n">
-        <v>6.009187426758122</v>
+        <v>5.876500230114136</v>
       </c>
       <c r="G58" t="n">
-        <v>0.6762579345495972</v>
+        <v>0.6903970084783125</v>
       </c>
       <c r="H58" t="n">
         <v>24</v>
@@ -1947,7 +1947,7 @@
         <v>45733</v>
       </c>
       <c r="B59" t="n">
-        <v>3.797525368092437</v>
+        <v>3.561750152120358</v>
       </c>
       <c r="C59" t="n">
         <v>24</v>
@@ -1956,13 +1956,13 @@
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>2.000909219230589</v>
+        <v>1.877010951140439</v>
       </c>
       <c r="F59" t="n">
-        <v>2.483298339886105</v>
+        <v>2.434175667284332</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.7292978871555644</v>
+        <v>-0.661559309270721</v>
       </c>
       <c r="H59" t="n">
         <v>24</v>
@@ -1973,7 +1973,7 @@
         <v>45734</v>
       </c>
       <c r="B60" t="n">
-        <v>3.200908453480115</v>
+        <v>2.955744453474777</v>
       </c>
       <c r="C60" t="n">
         <v>24</v>
@@ -1982,13 +1982,13 @@
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>1.648306169678642</v>
+        <v>1.511698754757565</v>
       </c>
       <c r="F60" t="n">
-        <v>1.875907650516155</v>
+        <v>1.797148947074609</v>
       </c>
       <c r="G60" t="n">
-        <v>-0.06827728085690632</v>
+        <v>0.0195414712422195</v>
       </c>
       <c r="H60" t="n">
         <v>24</v>
@@ -1999,7 +1999,7 @@
         <v>45735</v>
       </c>
       <c r="B61" t="n">
-        <v>3.948757048072494</v>
+        <v>3.884528026584269</v>
       </c>
       <c r="C61" t="n">
         <v>24</v>
@@ -2008,13 +2008,13 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>2.028423180238406</v>
+        <v>1.981016114109552</v>
       </c>
       <c r="F61" t="n">
-        <v>2.344440981208749</v>
+        <v>2.329138334530267</v>
       </c>
       <c r="G61" t="n">
-        <v>0.1097980762195524</v>
+        <v>0.1213812104288133</v>
       </c>
       <c r="H61" t="n">
         <v>24</v>
@@ -2025,7 +2025,7 @@
         <v>45736</v>
       </c>
       <c r="B62" t="n">
-        <v>2.462447787681126</v>
+        <v>2.370865649757516</v>
       </c>
       <c r="C62" t="n">
         <v>24</v>
@@ -2034,13 +2034,13 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>1.256795217808088</v>
+        <v>1.202698093110053</v>
       </c>
       <c r="F62" t="n">
-        <v>1.613725867575601</v>
+        <v>1.571840974116042</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.2205375005697485</v>
+        <v>-0.158000687794452</v>
       </c>
       <c r="H62" t="n">
         <v>24</v>
@@ -2051,7 +2051,7 @@
         <v>45737</v>
       </c>
       <c r="B63" t="n">
-        <v>2.791954375711901</v>
+        <v>2.492013872188031</v>
       </c>
       <c r="C63" t="n">
         <v>24</v>
@@ -2060,13 +2060,13 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>1.447491173330942</v>
+        <v>1.277374042330682</v>
       </c>
       <c r="F63" t="n">
-        <v>1.746045870893096</v>
+        <v>1.554754414724472</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.224114583000089</v>
+        <v>0.02941322125835988</v>
       </c>
       <c r="H63" t="n">
         <v>24</v>
@@ -2077,7 +2077,7 @@
         <v>45738</v>
       </c>
       <c r="B64" t="n">
-        <v>2.593877586741477</v>
+        <v>2.406652376758947</v>
       </c>
       <c r="C64" t="n">
         <v>24</v>
@@ -2086,13 +2086,13 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>1.314566990101337</v>
+        <v>1.207099576088444</v>
       </c>
       <c r="F64" t="n">
-        <v>1.577404152651923</v>
+        <v>1.482869145155338</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.5255819889226852</v>
+        <v>-0.3482028799302046</v>
       </c>
       <c r="H64" t="n">
         <v>24</v>
@@ -2103,7 +2103,7 @@
         <v>45739</v>
       </c>
       <c r="B65" t="n">
-        <v>2.802296791150027</v>
+        <v>2.760383301756662</v>
       </c>
       <c r="C65" t="n">
         <v>24</v>
@@ -2112,13 +2112,13 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>1.431597024209301</v>
+        <v>1.401990638771653</v>
       </c>
       <c r="F65" t="n">
-        <v>1.646115038981536</v>
+        <v>1.696175065984521</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.0664091479897102</v>
+        <v>-0.1322565613196178</v>
       </c>
       <c r="H65" t="n">
         <v>24</v>
@@ -2129,7 +2129,7 @@
         <v>45740</v>
       </c>
       <c r="B66" t="n">
-        <v>1.928363010569722</v>
+        <v>1.928776347455486</v>
       </c>
       <c r="C66" t="n">
         <v>24</v>
@@ -2138,13 +2138,13 @@
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>1.010194031890916</v>
+        <v>1.013042502964923</v>
       </c>
       <c r="F66" t="n">
-        <v>1.188238430819943</v>
+        <v>1.248165815928943</v>
       </c>
       <c r="G66" t="n">
-        <v>0.1082508569505256</v>
+        <v>0.01603402729724923</v>
       </c>
       <c r="H66" t="n">
         <v>24</v>
@@ -2155,7 +2155,7 @@
         <v>45741</v>
       </c>
       <c r="B67" t="n">
-        <v>3.760935169339279</v>
+        <v>3.942257033438611</v>
       </c>
       <c r="C67" t="n">
         <v>24</v>
@@ -2164,13 +2164,13 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>1.887236655315509</v>
+        <v>1.981480811140983</v>
       </c>
       <c r="F67" t="n">
-        <v>2.411573903647653</v>
+        <v>2.491571265538461</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.206671460147914</v>
+        <v>-0.2880553243676132</v>
       </c>
       <c r="H67" t="n">
         <v>24</v>
@@ -2181,7 +2181,7 @@
         <v>45742</v>
       </c>
       <c r="B68" t="n">
-        <v>3.961126214841663</v>
+        <v>3.676244869348114</v>
       </c>
       <c r="C68" t="n">
         <v>24</v>
@@ -2190,13 +2190,13 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>2.027171953956039</v>
+        <v>1.878888887261252</v>
       </c>
       <c r="F68" t="n">
-        <v>2.341125600738163</v>
+        <v>2.206786317557492</v>
       </c>
       <c r="G68" t="n">
-        <v>-0.2990816815587753</v>
+        <v>-0.1542704983251753</v>
       </c>
       <c r="H68" t="n">
         <v>24</v>
@@ -2207,7 +2207,7 @@
         <v>45743</v>
       </c>
       <c r="B69" t="n">
-        <v>3.638926871426929</v>
+        <v>3.527923015510773</v>
       </c>
       <c r="C69" t="n">
         <v>24</v>
@@ -2216,13 +2216,13 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>1.854725214051704</v>
+        <v>1.787823422078666</v>
       </c>
       <c r="F69" t="n">
-        <v>2.346632613959577</v>
+        <v>2.264355390694564</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.1232825695903064</v>
+        <v>-0.04589478143423187</v>
       </c>
       <c r="H69" t="n">
         <v>24</v>
@@ -2233,7 +2233,7 @@
         <v>45744</v>
       </c>
       <c r="B70" t="n">
-        <v>3.27509607879063</v>
+        <v>3.335398328980899</v>
       </c>
       <c r="C70" t="n">
         <v>24</v>
@@ -2242,13 +2242,13 @@
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>1.723576172953845</v>
+        <v>1.748804327028207</v>
       </c>
       <c r="F70" t="n">
-        <v>2.186685878985349</v>
+        <v>2.156756888287968</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.09034801536171222</v>
+        <v>-0.06070526400639809</v>
       </c>
       <c r="H70" t="n">
         <v>24</v>
@@ -2259,7 +2259,7 @@
         <v>45745</v>
       </c>
       <c r="B71" t="n">
-        <v>2.160905916699092</v>
+        <v>1.786274899602884</v>
       </c>
       <c r="C71" t="n">
         <v>24</v>
@@ -2268,13 +2268,13 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>1.117413401739671</v>
+        <v>0.9210570276267873</v>
       </c>
       <c r="F71" t="n">
-        <v>1.413842299156205</v>
+        <v>1.260040022177453</v>
       </c>
       <c r="G71" t="n">
-        <v>-0.07092136669476745</v>
+        <v>0.1494020699238664</v>
       </c>
       <c r="H71" t="n">
         <v>24</v>
@@ -2285,7 +2285,7 @@
         <v>45746</v>
       </c>
       <c r="B72" t="n">
-        <v>4.041313899173656</v>
+        <v>4.042386218953122</v>
       </c>
       <c r="C72" t="n">
         <v>24</v>
@@ -2294,13 +2294,13 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>2.128319866882762</v>
+        <v>2.132083849068298</v>
       </c>
       <c r="F72" t="n">
-        <v>2.521282598542429</v>
+        <v>2.485278209967671</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.4538701633155158</v>
+        <v>-0.4126435645411173</v>
       </c>
       <c r="H72" t="n">
         <v>24</v>
@@ -2311,7 +2311,7 @@
         <v>45747</v>
       </c>
       <c r="B73" t="n">
-        <v>2.986953879274521</v>
+        <v>2.759459771374704</v>
       </c>
       <c r="C73" t="n">
         <v>24</v>
@@ -2320,13 +2320,13 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>1.53769787169695</v>
+        <v>1.422138655172748</v>
       </c>
       <c r="F73" t="n">
-        <v>1.880156598489727</v>
+        <v>1.812649344389245</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.4591209123314859</v>
+        <v>-0.3562221467869731</v>
       </c>
       <c r="H73" t="n">
         <v>24</v>
@@ -2337,7 +2337,7 @@
         <v>45748</v>
       </c>
       <c r="B74" t="n">
-        <v>6.545679000031797</v>
+        <v>5.815438381734548</v>
       </c>
       <c r="C74" t="n">
         <v>24</v>
@@ -2346,13 +2346,13 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>2.050044398384604</v>
+        <v>1.815683043852946</v>
       </c>
       <c r="F74" t="n">
-        <v>5.348448135819113</v>
+        <v>5.34974430481401</v>
       </c>
       <c r="G74" t="n">
-        <v>0.7243620652508329</v>
+        <v>0.7242284501806489</v>
       </c>
       <c r="H74" t="n">
         <v>24</v>
@@ -2363,7 +2363,7 @@
         <v>45749</v>
       </c>
       <c r="B75" t="n">
-        <v>2.582685933390139</v>
+        <v>2.069236746634851</v>
       </c>
       <c r="C75" t="n">
         <v>24</v>
@@ -2372,13 +2372,13 @@
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>0.7814927133527273</v>
+        <v>0.6286757567403217</v>
       </c>
       <c r="F75" t="n">
-        <v>0.9822008316658689</v>
+        <v>0.7490283034774539</v>
       </c>
       <c r="G75" t="n">
-        <v>-0.8162104470665148</v>
+        <v>-0.05623859293592748</v>
       </c>
       <c r="H75" t="n">
         <v>24</v>
@@ -2389,7 +2389,7 @@
         <v>45750</v>
       </c>
       <c r="B76" t="n">
-        <v>2.238029344725216</v>
+        <v>2.347196997656127</v>
       </c>
       <c r="C76" t="n">
         <v>24</v>
@@ -2398,13 +2398,13 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>0.6723026106039374</v>
+        <v>0.6950285308584565</v>
       </c>
       <c r="F76" t="n">
-        <v>0.8236793283113886</v>
+        <v>0.8180319518736698</v>
       </c>
       <c r="G76" t="n">
-        <v>-0.2277326705806801</v>
+        <v>-0.2109550256505202</v>
       </c>
       <c r="H76" t="n">
         <v>24</v>
@@ -2415,7 +2415,7 @@
         <v>45751</v>
       </c>
       <c r="B77" t="n">
-        <v>3.069280386349158</v>
+        <v>2.440875470089414</v>
       </c>
       <c r="C77" t="n">
         <v>24</v>
@@ -2424,13 +2424,13 @@
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>0.9226281637518198</v>
+        <v>0.7368449653714896</v>
       </c>
       <c r="F77" t="n">
-        <v>1.16935128730096</v>
+        <v>0.9362830066627418</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.8937921973037641</v>
+        <v>-0.2141060098783301</v>
       </c>
       <c r="H77" t="n">
         <v>24</v>
@@ -2441,7 +2441,7 @@
         <v>45752</v>
       </c>
       <c r="B78" t="n">
-        <v>3.244905951964524</v>
+        <v>1.98278116712646</v>
       </c>
       <c r="C78" t="n">
         <v>24</v>
@@ -2450,13 +2450,13 @@
         <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>0.9780879246852513</v>
+        <v>0.5952689194910229</v>
       </c>
       <c r="F78" t="n">
-        <v>1.137854600655249</v>
+        <v>0.6735096182580107</v>
       </c>
       <c r="G78" t="n">
-        <v>-1.508604974104385</v>
+        <v>0.121086077956376</v>
       </c>
       <c r="H78" t="n">
         <v>24</v>
@@ -2467,7 +2467,7 @@
         <v>45753</v>
       </c>
       <c r="B79" t="n">
-        <v>3.264454437930416</v>
+        <v>2.285155645212453</v>
       </c>
       <c r="C79" t="n">
         <v>24</v>
@@ -2476,13 +2476,13 @@
         <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>0.9858425831962455</v>
+        <v>0.6879270671047268</v>
       </c>
       <c r="F79" t="n">
-        <v>1.285845900412711</v>
+        <v>0.9185956751034066</v>
       </c>
       <c r="G79" t="n">
-        <v>-1.508698572600375</v>
+        <v>-0.2803226431962456</v>
       </c>
       <c r="H79" t="n">
         <v>24</v>
@@ -2493,7 +2493,7 @@
         <v>45754</v>
       </c>
       <c r="B80" t="n">
-        <v>2.849350312559802</v>
+        <v>1.803876078558025</v>
       </c>
       <c r="C80" t="n">
         <v>24</v>
@@ -2502,13 +2502,13 @@
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>0.8650680150277754</v>
+        <v>0.5501221649505195</v>
       </c>
       <c r="F80" t="n">
-        <v>1.016410111769382</v>
+        <v>0.7124532777125258</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.9467542330572774</v>
+        <v>0.04349784817442082</v>
       </c>
       <c r="H80" t="n">
         <v>24</v>
@@ -2519,7 +2519,7 @@
         <v>45755</v>
       </c>
       <c r="B81" t="n">
-        <v>11.88836797402403</v>
+        <v>11.52566410973955</v>
       </c>
       <c r="C81" t="n">
         <v>24</v>
@@ -2528,13 +2528,13 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>2.793216976105469</v>
+        <v>2.602245923370868</v>
       </c>
       <c r="F81" t="n">
-        <v>5.666067788162215</v>
+        <v>5.483106550190415</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.8209331368634412</v>
+        <v>-0.7052334286384494</v>
       </c>
       <c r="H81" t="n">
         <v>24</v>
@@ -2545,7 +2545,7 @@
         <v>45756</v>
       </c>
       <c r="B82" t="n">
-        <v>2.619586758094383</v>
+        <v>2.061572400413219</v>
       </c>
       <c r="C82" t="n">
         <v>24</v>
@@ -2554,13 +2554,13 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0.7938258477597029</v>
+        <v>0.6240195204451684</v>
       </c>
       <c r="F82" t="n">
-        <v>0.9562083834232493</v>
+        <v>0.7601267001039466</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.7065623578701234</v>
+        <v>-0.07842275644340702</v>
       </c>
       <c r="H82" t="n">
         <v>24</v>
@@ -2571,7 +2571,7 @@
         <v>45757</v>
       </c>
       <c r="B83" t="n">
-        <v>3.369369144613795</v>
+        <v>2.548487399867214</v>
       </c>
       <c r="C83" t="n">
         <v>23</v>
@@ -2580,13 +2580,13 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>1.026951718225979</v>
+        <v>0.7751804152794513</v>
       </c>
       <c r="F83" t="n">
-        <v>1.186794865086372</v>
+        <v>0.8859565978012492</v>
       </c>
       <c r="G83" t="n">
-        <v>-1.04419572912707</v>
+        <v>-0.1391897084943574</v>
       </c>
       <c r="H83" t="n">
         <v>23</v>

--- a/optimized_version/metadata/validation_daily_metrics/agus1_validation_daily_metrics.xlsx
+++ b/optimized_version/metadata/validation_daily_metrics/agus1_validation_daily_metrics.xlsx
@@ -467,7 +467,7 @@
         <v>45676</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2651453140345938</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -476,10 +476,10 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1605521162807975</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1605521162807975</v>
+        <v>0</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
@@ -491,7 +491,7 @@
         <v>45677</v>
       </c>
       <c r="B3" t="n">
-        <v>2.430540361702775</v>
+        <v>2.766190002843199</v>
       </c>
       <c r="C3" t="n">
         <v>24</v>
@@ -500,13 +500,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1.42273464557825</v>
+        <v>1.625353618494352</v>
       </c>
       <c r="F3" t="n">
-        <v>1.815387828360864</v>
+        <v>2.053659880011184</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.09692654532376932</v>
+        <v>-0.4037693170533396</v>
       </c>
       <c r="H3" t="n">
         <v>24</v>
@@ -517,7 +517,7 @@
         <v>45678</v>
       </c>
       <c r="B4" t="n">
-        <v>5.865560239059886</v>
+        <v>5.989011369747502</v>
       </c>
       <c r="C4" t="n">
         <v>24</v>
@@ -526,13 +526,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>2.928355730715861</v>
+        <v>2.99262428562448</v>
       </c>
       <c r="F4" t="n">
-        <v>4.809888979542398</v>
+        <v>4.73543120471401</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4794674004172672</v>
+        <v>0.4954585020287156</v>
       </c>
       <c r="H4" t="n">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>45679</v>
       </c>
       <c r="B5" t="n">
-        <v>2.197674143940761</v>
+        <v>2.444268743254129</v>
       </c>
       <c r="C5" t="n">
         <v>24</v>
@@ -552,13 +552,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1.295098015277056</v>
+        <v>1.443367379776679</v>
       </c>
       <c r="F5" t="n">
-        <v>1.752634824723558</v>
+        <v>2.001118025407219</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.03763644775676322</v>
+        <v>-0.3527195059332329</v>
       </c>
       <c r="H5" t="n">
         <v>24</v>
@@ -569,7 +569,7 @@
         <v>45680</v>
       </c>
       <c r="B6" t="n">
-        <v>2.459964525892394</v>
+        <v>2.661797399166768</v>
       </c>
       <c r="C6" t="n">
         <v>24</v>
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1.454574012407956</v>
+        <v>1.574241850589054</v>
       </c>
       <c r="F6" t="n">
-        <v>1.62450045970233</v>
+        <v>1.818221982315451</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05260039300714414</v>
+        <v>-0.1868267633544785</v>
       </c>
       <c r="H6" t="n">
         <v>24</v>
@@ -595,7 +595,7 @@
         <v>45681</v>
       </c>
       <c r="B7" t="n">
-        <v>2.740801888593122</v>
+        <v>2.936451785329262</v>
       </c>
       <c r="C7" t="n">
         <v>24</v>
@@ -604,13 +604,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1.626698651694603</v>
+        <v>1.745131254600828</v>
       </c>
       <c r="F7" t="n">
-        <v>2.297955766563221</v>
+        <v>2.445359235463014</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3063719502882696</v>
+        <v>-0.4793429074064044</v>
       </c>
       <c r="H7" t="n">
         <v>24</v>
@@ -621,7 +621,7 @@
         <v>45682</v>
       </c>
       <c r="B8" t="n">
-        <v>4.550766499223617</v>
+        <v>4.72204172103785</v>
       </c>
       <c r="C8" t="n">
         <v>24</v>
@@ -630,13 +630,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>2.265839895435322</v>
+        <v>2.311507784631538</v>
       </c>
       <c r="F8" t="n">
-        <v>4.606726436407526</v>
+        <v>4.579672689100842</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5633449845175875</v>
+        <v>0.5684585797266843</v>
       </c>
       <c r="H8" t="n">
         <v>24</v>
@@ -647,7 +647,7 @@
         <v>45683</v>
       </c>
       <c r="B9" t="n">
-        <v>4.229880624963123</v>
+        <v>3.691411544894802</v>
       </c>
       <c r="C9" t="n">
         <v>24</v>
@@ -656,13 +656,13 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>2.416967829681993</v>
+        <v>2.156672256659099</v>
       </c>
       <c r="F9" t="n">
-        <v>3.612245593713946</v>
+        <v>3.322318650053953</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3127543724525795</v>
+        <v>0.4186468717486761</v>
       </c>
       <c r="H9" t="n">
         <v>24</v>
@@ -673,7 +673,7 @@
         <v>45684</v>
       </c>
       <c r="B10" t="n">
-        <v>3.020136644679959</v>
+        <v>2.823689975365849</v>
       </c>
       <c r="C10" t="n">
         <v>24</v>
@@ -682,13 +682,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>1.832992502745777</v>
+        <v>1.715920848753535</v>
       </c>
       <c r="F10" t="n">
-        <v>2.451717769647957</v>
+        <v>2.319039202935248</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6135727925701586</v>
+        <v>-0.4436562440099114</v>
       </c>
       <c r="H10" t="n">
         <v>24</v>
@@ -699,7 +699,7 @@
         <v>45685</v>
       </c>
       <c r="B11" t="n">
-        <v>2.194660047520419</v>
+        <v>2.350638130082778</v>
       </c>
       <c r="C11" t="n">
         <v>24</v>
@@ -708,13 +708,13 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>1.341499841975032</v>
+        <v>1.436994092336359</v>
       </c>
       <c r="F11" t="n">
-        <v>1.581610910479519</v>
+        <v>1.617931733696412</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.03585485500751462</v>
+        <v>-0.08397680170030708</v>
       </c>
       <c r="H11" t="n">
         <v>24</v>
@@ -725,7 +725,7 @@
         <v>45686</v>
       </c>
       <c r="B12" t="n">
-        <v>2.22211616218984</v>
+        <v>2.174522961971473</v>
       </c>
       <c r="C12" t="n">
         <v>24</v>
@@ -734,13 +734,13 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1.329461757237712</v>
+        <v>1.302806173168935</v>
       </c>
       <c r="F12" t="n">
-        <v>1.576903954182576</v>
+        <v>1.600628227795222</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.150274943773429</v>
+        <v>-0.1851467190449858</v>
       </c>
       <c r="H12" t="n">
         <v>24</v>
@@ -751,7 +751,7 @@
         <v>45687</v>
       </c>
       <c r="B13" t="n">
-        <v>2.068458202359058</v>
+        <v>2.035070193862242</v>
       </c>
       <c r="C13" t="n">
         <v>24</v>
@@ -760,13 +760,13 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1.243626714988654</v>
+        <v>1.224357888657809</v>
       </c>
       <c r="F13" t="n">
-        <v>1.525292614803108</v>
+        <v>1.528368734204516</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.3983197409313997</v>
+        <v>-0.4039655243633062</v>
       </c>
       <c r="H13" t="n">
         <v>24</v>
@@ -777,7 +777,7 @@
         <v>45688</v>
       </c>
       <c r="B14" t="n">
-        <v>5.154420104354513</v>
+        <v>5.104892856827624</v>
       </c>
       <c r="C14" t="n">
         <v>24</v>
@@ -786,13 +786,13 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>2.685438523945093</v>
+        <v>2.660552958753571</v>
       </c>
       <c r="F14" t="n">
-        <v>4.667438150031456</v>
+        <v>4.343909987401323</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4635208112398838</v>
+        <v>0.5353163726042391</v>
       </c>
       <c r="H14" t="n">
         <v>24</v>
@@ -803,7 +803,7 @@
         <v>45689</v>
       </c>
       <c r="B15" t="n">
-        <v>5.187860389787174</v>
+        <v>5.430305854525485</v>
       </c>
       <c r="C15" t="n">
         <v>24</v>
@@ -812,13 +812,13 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>2.797033956037293</v>
+        <v>2.917579088012751</v>
       </c>
       <c r="F15" t="n">
-        <v>4.714957355833723</v>
+        <v>4.646528640098296</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5347808455160468</v>
+        <v>0.5481864138444629</v>
       </c>
       <c r="H15" t="n">
         <v>24</v>
@@ -829,7 +829,7 @@
         <v>45690</v>
       </c>
       <c r="B16" t="n">
-        <v>3.360442291631342</v>
+        <v>3.276325942023282</v>
       </c>
       <c r="C16" t="n">
         <v>24</v>
@@ -838,13 +838,13 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>1.900031507844793</v>
+        <v>1.858092108809291</v>
       </c>
       <c r="F16" t="n">
-        <v>3.117571475491665</v>
+        <v>2.962940314088081</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1345958870976622</v>
+        <v>0.2183147400164789</v>
       </c>
       <c r="H16" t="n">
         <v>24</v>
@@ -855,7 +855,7 @@
         <v>45691</v>
       </c>
       <c r="B17" t="n">
-        <v>2.554464894758206</v>
+        <v>2.493985658872644</v>
       </c>
       <c r="C17" t="n">
         <v>24</v>
@@ -864,13 +864,13 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1.559296275016673</v>
+        <v>1.525281320554537</v>
       </c>
       <c r="F17" t="n">
-        <v>1.778727748578241</v>
+        <v>1.777677938515938</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1145369541615833</v>
+        <v>-0.1132217367808253</v>
       </c>
       <c r="H17" t="n">
         <v>24</v>
@@ -881,7 +881,7 @@
         <v>45692</v>
       </c>
       <c r="B18" t="n">
-        <v>2.774100158653907</v>
+        <v>3.007484936735889</v>
       </c>
       <c r="C18" t="n">
         <v>24</v>
@@ -890,13 +890,13 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>1.645724545563917</v>
+        <v>1.800721442710886</v>
       </c>
       <c r="F18" t="n">
-        <v>1.961566155182006</v>
+        <v>2.215729951632348</v>
       </c>
       <c r="G18" t="n">
-        <v>0.09929203614601323</v>
+        <v>-0.1492426643676728</v>
       </c>
       <c r="H18" t="n">
         <v>24</v>
@@ -907,7 +907,7 @@
         <v>45693</v>
       </c>
       <c r="B19" t="n">
-        <v>2.426608600140221</v>
+        <v>2.575034816682507</v>
       </c>
       <c r="C19" t="n">
         <v>24</v>
@@ -916,13 +916,13 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4893848210238</v>
+        <v>1.584014562036767</v>
       </c>
       <c r="F19" t="n">
-        <v>1.658537380460651</v>
+        <v>1.792786286258835</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.132084846594833</v>
+        <v>-0.3227735180743434</v>
       </c>
       <c r="H19" t="n">
         <v>24</v>
@@ -933,7 +933,7 @@
         <v>45694</v>
       </c>
       <c r="B20" t="n">
-        <v>3.692959864468021</v>
+        <v>4.183551584253822</v>
       </c>
       <c r="C20" t="n">
         <v>24</v>
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>2.117703001042465</v>
+        <v>2.420426734128911</v>
       </c>
       <c r="F20" t="n">
-        <v>2.922387150044489</v>
+        <v>3.397841565720874</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.09282767638201439</v>
+        <v>-0.4773467310711512</v>
       </c>
       <c r="H20" t="n">
         <v>24</v>
@@ -959,7 +959,7 @@
         <v>45695</v>
       </c>
       <c r="B21" t="n">
-        <v>2.972030093138595</v>
+        <v>3.195514234997796</v>
       </c>
       <c r="C21" t="n">
         <v>24</v>
@@ -968,13 +968,13 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>1.784550356641019</v>
+        <v>1.926644608250316</v>
       </c>
       <c r="F21" t="n">
-        <v>1.993958045758039</v>
+        <v>2.268049883990807</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.05810581944176829</v>
+        <v>-0.3689963023472254</v>
       </c>
       <c r="H21" t="n">
         <v>24</v>
@@ -985,7 +985,7 @@
         <v>45696</v>
       </c>
       <c r="B22" t="n">
-        <v>5.701639514960433</v>
+        <v>5.874983910826556</v>
       </c>
       <c r="C22" t="n">
         <v>24</v>
@@ -994,13 +994,13 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>3.033259213382616</v>
+        <v>3.124825474025608</v>
       </c>
       <c r="F22" t="n">
-        <v>4.511896593210951</v>
+        <v>4.502548794063526</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3494727854048207</v>
+        <v>0.3521655325793245</v>
       </c>
       <c r="H22" t="n">
         <v>24</v>
@@ -1011,7 +1011,7 @@
         <v>45697</v>
       </c>
       <c r="B23" t="n">
-        <v>8.588206154643196</v>
+        <v>8.835875353325072</v>
       </c>
       <c r="C23" t="n">
         <v>24</v>
@@ -1020,13 +1020,13 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>4.313669982235568</v>
+        <v>4.455697808668099</v>
       </c>
       <c r="F23" t="n">
-        <v>7.476634821926305</v>
+        <v>7.537465662563805</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.5789654367493091</v>
+        <v>-0.6047632813020041</v>
       </c>
       <c r="H23" t="n">
         <v>24</v>
@@ -1037,7 +1037,7 @@
         <v>45698</v>
       </c>
       <c r="B24" t="n">
-        <v>1.81979954934535</v>
+        <v>1.667133893558897</v>
       </c>
       <c r="C24" t="n">
         <v>24</v>
@@ -1046,13 +1046,13 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>1.092256651051292</v>
+        <v>1.003953151362055</v>
       </c>
       <c r="F24" t="n">
-        <v>1.508304810976753</v>
+        <v>1.413920623104461</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.07978956479527599</v>
+        <v>0.05112074577169756</v>
       </c>
       <c r="H24" t="n">
         <v>24</v>
@@ -1063,7 +1063,7 @@
         <v>45699</v>
       </c>
       <c r="B25" t="n">
-        <v>2.607769989153638</v>
+        <v>2.7188074535587</v>
       </c>
       <c r="C25" t="n">
         <v>24</v>
@@ -1072,13 +1072,13 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>1.553249209059296</v>
+        <v>1.618933092197431</v>
       </c>
       <c r="F25" t="n">
-        <v>1.822773657895624</v>
+        <v>1.919927551770465</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.2715718200990895</v>
+        <v>-0.4107338568909815</v>
       </c>
       <c r="H25" t="n">
         <v>24</v>
@@ -1089,7 +1089,7 @@
         <v>45700</v>
       </c>
       <c r="B26" t="n">
-        <v>2.323416432345348</v>
+        <v>2.470111223444101</v>
       </c>
       <c r="C26" t="n">
         <v>24</v>
@@ -1098,13 +1098,13 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>1.399022655697928</v>
+        <v>1.486088413437596</v>
       </c>
       <c r="F26" t="n">
-        <v>1.767801068802932</v>
+        <v>1.856665496149451</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.1488329089806024</v>
+        <v>-0.2672357512611334</v>
       </c>
       <c r="H26" t="n">
         <v>24</v>
@@ -1115,7 +1115,7 @@
         <v>45701</v>
       </c>
       <c r="B27" t="n">
-        <v>2.15026146040755</v>
+        <v>2.343463383295104</v>
       </c>
       <c r="C27" t="n">
         <v>24</v>
@@ -1124,13 +1124,13 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>1.298835851557633</v>
+        <v>1.414833732784986</v>
       </c>
       <c r="F27" t="n">
-        <v>1.568641109500625</v>
+        <v>1.656311327747677</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.1693215752930477</v>
+        <v>-0.3036791574106348</v>
       </c>
       <c r="H27" t="n">
         <v>24</v>
@@ -1141,7 +1141,7 @@
         <v>45702</v>
       </c>
       <c r="B28" t="n">
-        <v>7.045113067368409</v>
+        <v>6.833900844670046</v>
       </c>
       <c r="C28" t="n">
         <v>24</v>
@@ -1150,13 +1150,13 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>2.33831798472007</v>
+        <v>2.263139395065116</v>
       </c>
       <c r="F28" t="n">
-        <v>6.322834785308451</v>
+        <v>6.208353095953513</v>
       </c>
       <c r="G28" t="n">
-        <v>0.791170873685732</v>
+        <v>0.798664562847949</v>
       </c>
       <c r="H28" t="n">
         <v>24</v>
@@ -1167,7 +1167,7 @@
         <v>45703</v>
       </c>
       <c r="B29" t="n">
-        <v>3.162551002641772</v>
+        <v>3.238933591427119</v>
       </c>
       <c r="C29" t="n">
         <v>24</v>
@@ -1176,13 +1176,13 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0.930351340734214</v>
+        <v>0.9529541666666668</v>
       </c>
       <c r="F29" t="n">
-        <v>1.101948169802134</v>
+        <v>1.131476846276471</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.08694402448506477</v>
+        <v>-0.145977751314649</v>
       </c>
       <c r="H29" t="n">
         <v>24</v>
@@ -1193,7 +1193,7 @@
         <v>45704</v>
       </c>
       <c r="B30" t="n">
-        <v>5.382986573315294</v>
+        <v>5.179591449143865</v>
       </c>
       <c r="C30" t="n">
         <v>24</v>
@@ -1202,13 +1202,13 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>2.248617361842699</v>
+        <v>2.111671346850902</v>
       </c>
       <c r="F30" t="n">
-        <v>4.51899758366046</v>
+        <v>4.034181482291011</v>
       </c>
       <c r="G30" t="n">
-        <v>0.8909174658560577</v>
+        <v>0.9130675611850916</v>
       </c>
       <c r="H30" t="n">
         <v>24</v>
@@ -1219,7 +1219,7 @@
         <v>45705</v>
       </c>
       <c r="B31" t="n">
-        <v>0.1222593645483517</v>
+        <v>1.155209658482554e-05</v>
       </c>
       <c r="C31" t="n">
         <v>24</v>
@@ -1228,13 +1228,13 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0.07344694442041622</v>
+        <v>6.939575541764498e-06</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1015120111254849</v>
+        <v>1.256205790627106e-05</v>
       </c>
       <c r="G31" t="n">
-        <v>-1316.605912813979</v>
+        <v>0.9999798222724745</v>
       </c>
       <c r="H31" t="n">
         <v>24</v>
@@ -1245,7 +1245,7 @@
         <v>45706</v>
       </c>
       <c r="B32" t="n">
-        <v>3.092037551234939</v>
+        <v>3.699009304276932</v>
       </c>
       <c r="C32" t="n">
         <v>24</v>
@@ -1254,13 +1254,13 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>1.781950078215914</v>
+        <v>2.13244356529595</v>
       </c>
       <c r="F32" t="n">
-        <v>2.165117061495862</v>
+        <v>2.505780918926996</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.6340334595737549</v>
+        <v>-1.188690617489749</v>
       </c>
       <c r="H32" t="n">
         <v>24</v>
@@ -1271,7 +1271,7 @@
         <v>45707</v>
       </c>
       <c r="B33" t="n">
-        <v>2.410627219953441</v>
+        <v>2.916040486988576</v>
       </c>
       <c r="C33" t="n">
         <v>24</v>
@@ -1280,13 +1280,13 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>1.386181989353507</v>
+        <v>1.69040353943428</v>
       </c>
       <c r="F33" t="n">
-        <v>1.812141063092033</v>
+        <v>2.090873787379043</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.3758763854733675</v>
+        <v>-0.8316860999722584</v>
       </c>
       <c r="H33" t="n">
         <v>24</v>
@@ -1297,7 +1297,7 @@
         <v>45708</v>
       </c>
       <c r="B34" t="n">
-        <v>3.625509502613846</v>
+        <v>3.883065313317508</v>
       </c>
       <c r="C34" t="n">
         <v>24</v>
@@ -1306,13 +1306,13 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>2.007217171344636</v>
+        <v>2.149426878605314</v>
       </c>
       <c r="F34" t="n">
-        <v>2.861914243206598</v>
+        <v>2.921200348861753</v>
       </c>
       <c r="G34" t="n">
-        <v>0.115649118548322</v>
+        <v>0.07862999754591282</v>
       </c>
       <c r="H34" t="n">
         <v>24</v>
@@ -1323,7 +1323,7 @@
         <v>45709</v>
       </c>
       <c r="B35" t="n">
-        <v>3.417966706208692</v>
+        <v>4.015796115180756</v>
       </c>
       <c r="C35" t="n">
         <v>24</v>
@@ -1332,13 +1332,13 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>1.955898392400645</v>
+        <v>2.298310292498973</v>
       </c>
       <c r="F35" t="n">
-        <v>2.429363457594341</v>
+        <v>2.848675087550745</v>
       </c>
       <c r="G35" t="n">
-        <v>-1.038544133844447</v>
+        <v>-1.802986230055495</v>
       </c>
       <c r="H35" t="n">
         <v>24</v>
@@ -1349,7 +1349,7 @@
         <v>45710</v>
       </c>
       <c r="B36" t="n">
-        <v>2.709026285533818</v>
+        <v>3.15072920641401</v>
       </c>
       <c r="C36" t="n">
         <v>24</v>
@@ -1358,13 +1358,13 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>1.554559225797681</v>
+        <v>1.814248315588533</v>
       </c>
       <c r="F36" t="n">
-        <v>2.202126331608276</v>
+        <v>2.658680576140674</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.8584345945189391</v>
+        <v>-1.708913557057414</v>
       </c>
       <c r="H36" t="n">
         <v>24</v>
@@ -1375,7 +1375,7 @@
         <v>45711</v>
       </c>
       <c r="B37" t="n">
-        <v>2.817709329262093</v>
+        <v>2.724654256745819</v>
       </c>
       <c r="C37" t="n">
         <v>24</v>
@@ -1384,13 +1384,13 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>1.616495454665303</v>
+        <v>1.567193245603393</v>
       </c>
       <c r="F37" t="n">
-        <v>1.939229739772333</v>
+        <v>1.954091163364547</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.7823357578132988</v>
+        <v>-0.8097585459853756</v>
       </c>
       <c r="H37" t="n">
         <v>24</v>
@@ -1401,7 +1401,7 @@
         <v>45712</v>
       </c>
       <c r="B38" t="n">
-        <v>4.256244259216794</v>
+        <v>4.838027506887309</v>
       </c>
       <c r="C38" t="n">
         <v>24</v>
@@ -1410,13 +1410,13 @@
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>2.118997336136558</v>
+        <v>2.42818641850381</v>
       </c>
       <c r="F38" t="n">
-        <v>3.486410955003449</v>
+        <v>3.547164937624684</v>
       </c>
       <c r="G38" t="n">
-        <v>0.7345495283985404</v>
+        <v>0.7252174736791166</v>
       </c>
       <c r="H38" t="n">
         <v>24</v>
@@ -1427,7 +1427,7 @@
         <v>45713</v>
       </c>
       <c r="B39" t="n">
-        <v>3.385865419858266</v>
+        <v>3.477303674632817</v>
       </c>
       <c r="C39" t="n">
         <v>24</v>
@@ -1436,13 +1436,13 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>1.784352977827181</v>
+        <v>1.791531132872164</v>
       </c>
       <c r="F39" t="n">
-        <v>2.776911564218472</v>
+        <v>2.663134899716785</v>
       </c>
       <c r="G39" t="n">
-        <v>0.8606762018670876</v>
+        <v>0.871859168111849</v>
       </c>
       <c r="H39" t="n">
         <v>24</v>
@@ -1453,7 +1453,7 @@
         <v>45714</v>
       </c>
       <c r="B40" t="n">
-        <v>2.107155023032368</v>
+        <v>2.146968633576725</v>
       </c>
       <c r="C40" t="n">
         <v>24</v>
@@ -1462,13 +1462,13 @@
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>1.266828654727789</v>
+        <v>1.290876749309245</v>
       </c>
       <c r="F40" t="n">
-        <v>1.560068954701052</v>
+        <v>1.653599741915465</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.2312251536853736</v>
+        <v>-0.3832818612436637</v>
       </c>
       <c r="H40" t="n">
         <v>24</v>
@@ -1479,7 +1479,7 @@
         <v>45715</v>
       </c>
       <c r="B41" t="n">
-        <v>2.19825495864946</v>
+        <v>2.155291669395436</v>
       </c>
       <c r="C41" t="n">
         <v>24</v>
@@ -1488,13 +1488,13 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>1.318803818607569</v>
+        <v>1.291459446500835</v>
       </c>
       <c r="F41" t="n">
-        <v>1.599513671135938</v>
+        <v>1.629898843595877</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.2549051486470071</v>
+        <v>-0.3030356314291993</v>
       </c>
       <c r="H41" t="n">
         <v>24</v>
@@ -1505,7 +1505,7 @@
         <v>45716</v>
       </c>
       <c r="B42" t="n">
-        <v>1.729793393668086</v>
+        <v>1.477972012756466</v>
       </c>
       <c r="C42" t="n">
         <v>24</v>
@@ -1514,13 +1514,13 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>1.042511115160863</v>
+        <v>0.8987390466949208</v>
       </c>
       <c r="F42" t="n">
-        <v>1.353731138305385</v>
+        <v>1.410417784395556</v>
       </c>
       <c r="G42" t="n">
-        <v>0.1958562516994606</v>
+        <v>0.1271001804879034</v>
       </c>
       <c r="H42" t="n">
         <v>24</v>
@@ -1531,7 +1531,7 @@
         <v>45717</v>
       </c>
       <c r="B43" t="n">
-        <v>2.588876052386084</v>
+        <v>2.38753420005592</v>
       </c>
       <c r="C43" t="n">
         <v>24</v>
@@ -1540,13 +1540,13 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>1.581603245016603</v>
+        <v>1.459482181256791</v>
       </c>
       <c r="F43" t="n">
-        <v>1.887935122205107</v>
+        <v>1.760761642111922</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.2403802775443158</v>
+        <v>-0.07890165067270782</v>
       </c>
       <c r="H43" t="n">
         <v>24</v>
@@ -1557,7 +1557,7 @@
         <v>45718</v>
       </c>
       <c r="B44" t="n">
-        <v>3.205248544505575</v>
+        <v>2.537714809572147</v>
       </c>
       <c r="C44" t="n">
         <v>24</v>
@@ -1566,13 +1566,13 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>1.799628174752714</v>
+        <v>1.461732055363177</v>
       </c>
       <c r="F44" t="n">
-        <v>2.394454029902274</v>
+        <v>1.992933383406725</v>
       </c>
       <c r="G44" t="n">
-        <v>0.568121537535583</v>
+        <v>0.700818935283785</v>
       </c>
       <c r="H44" t="n">
         <v>24</v>
@@ -1583,7 +1583,7 @@
         <v>45719</v>
       </c>
       <c r="B45" t="n">
-        <v>3.072058164696779</v>
+        <v>3.106736423625797</v>
       </c>
       <c r="C45" t="n">
         <v>24</v>
@@ -1592,13 +1592,13 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>1.858334429064595</v>
+        <v>1.877286751801679</v>
       </c>
       <c r="F45" t="n">
-        <v>2.096014675706787</v>
+        <v>2.123827721879781</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.1071106756930493</v>
+        <v>-0.1366872035392419</v>
       </c>
       <c r="H45" t="n">
         <v>24</v>
@@ -1609,7 +1609,7 @@
         <v>45720</v>
       </c>
       <c r="B46" t="n">
-        <v>4.770138857879188</v>
+        <v>4.475343174683976</v>
       </c>
       <c r="C46" t="n">
         <v>24</v>
@@ -1618,13 +1618,13 @@
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>2.530668036053889</v>
+        <v>2.395816002267923</v>
       </c>
       <c r="F46" t="n">
-        <v>2.964298766597821</v>
+        <v>2.873214552880612</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.755952881432179</v>
+        <v>-0.649700197386357</v>
       </c>
       <c r="H46" t="n">
         <v>24</v>
@@ -1635,7 +1635,7 @@
         <v>45721</v>
       </c>
       <c r="B47" t="n">
-        <v>2.557822971148153</v>
+        <v>3.055836579028981</v>
       </c>
       <c r="C47" t="n">
         <v>24</v>
@@ -1644,13 +1644,13 @@
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>1.395151730019412</v>
+        <v>1.662171188442782</v>
       </c>
       <c r="F47" t="n">
-        <v>1.692685328340578</v>
+        <v>2.073240874495368</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.8236015401901839</v>
+        <v>-1.73575382753639</v>
       </c>
       <c r="H47" t="n">
         <v>24</v>
@@ -1661,7 +1661,7 @@
         <v>45722</v>
       </c>
       <c r="B48" t="n">
-        <v>2.870083981603737</v>
+        <v>3.256740656873249</v>
       </c>
       <c r="C48" t="n">
         <v>24</v>
@@ -1670,13 +1670,13 @@
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>1.541082703570525</v>
+        <v>1.748221945375438</v>
       </c>
       <c r="F48" t="n">
-        <v>1.988425198620724</v>
+        <v>2.086334763838389</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.4151400678973891</v>
+        <v>-0.5579334445623052</v>
       </c>
       <c r="H48" t="n">
         <v>24</v>
@@ -1687,7 +1687,7 @@
         <v>45723</v>
       </c>
       <c r="B49" t="n">
-        <v>2.954196767516499</v>
+        <v>3.819732411659619</v>
       </c>
       <c r="C49" t="n">
         <v>24</v>
@@ -1696,13 +1696,13 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>1.607245837382349</v>
+        <v>2.069798686839755</v>
       </c>
       <c r="F49" t="n">
-        <v>2.167206951311162</v>
+        <v>2.729338630691386</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.7257712198659616</v>
+        <v>-1.73714179659684</v>
       </c>
       <c r="H49" t="n">
         <v>24</v>
@@ -1713,7 +1713,7 @@
         <v>45724</v>
       </c>
       <c r="B50" t="n">
-        <v>3.134300368970681</v>
+        <v>4.340430195315472</v>
       </c>
       <c r="C50" t="n">
         <v>24</v>
@@ -1722,13 +1722,13 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>1.701076213022384</v>
+        <v>2.370141457899932</v>
       </c>
       <c r="F50" t="n">
-        <v>2.069357096774002</v>
+        <v>2.777571291424685</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.5369535936220329</v>
+        <v>-1.768983083981611</v>
       </c>
       <c r="H50" t="n">
         <v>24</v>
@@ -1739,7 +1739,7 @@
         <v>45725</v>
       </c>
       <c r="B51" t="n">
-        <v>2.984738251409545</v>
+        <v>3.898776213662774</v>
       </c>
       <c r="C51" t="n">
         <v>24</v>
@@ -1748,13 +1748,13 @@
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>1.627180416101279</v>
+        <v>2.130292363998116</v>
       </c>
       <c r="F51" t="n">
-        <v>2.005455018598045</v>
+        <v>2.705809693362055</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.3249451154348144</v>
+        <v>-1.411940189725896</v>
       </c>
       <c r="H51" t="n">
         <v>24</v>
@@ -1765,7 +1765,7 @@
         <v>45726</v>
       </c>
       <c r="B52" t="n">
-        <v>2.477406472092433</v>
+        <v>3.414993561261691</v>
       </c>
       <c r="C52" t="n">
         <v>24</v>
@@ -1774,13 +1774,13 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>1.340563185528725</v>
+        <v>1.851533024470748</v>
       </c>
       <c r="F52" t="n">
-        <v>1.583540436128894</v>
+        <v>2.205251752582028</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.3531018556090377</v>
+        <v>-1.624149213217464</v>
       </c>
       <c r="H52" t="n">
         <v>24</v>
@@ -1791,7 +1791,7 @@
         <v>45727</v>
       </c>
       <c r="B53" t="n">
-        <v>3.037438238589651</v>
+        <v>3.532450366050487</v>
       </c>
       <c r="C53" t="n">
         <v>24</v>
@@ -1800,13 +1800,13 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>1.621454690976751</v>
+        <v>1.890609981927183</v>
       </c>
       <c r="F53" t="n">
-        <v>1.899261378365145</v>
+        <v>2.27107139789846</v>
       </c>
       <c r="G53" t="n">
-        <v>0.01719975736109114</v>
+        <v>-0.4052621753127059</v>
       </c>
       <c r="H53" t="n">
         <v>24</v>
@@ -1817,7 +1817,7 @@
         <v>45728</v>
       </c>
       <c r="B54" t="n">
-        <v>3.7680050300002</v>
+        <v>3.88408654415792</v>
       </c>
       <c r="C54" t="n">
         <v>24</v>
@@ -1826,13 +1826,13 @@
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>1.888771907276769</v>
+        <v>1.948235202185679</v>
       </c>
       <c r="F54" t="n">
-        <v>2.342191142732228</v>
+        <v>2.287812253373685</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.3463316058067092</v>
+        <v>-0.2845414891129068</v>
       </c>
       <c r="H54" t="n">
         <v>24</v>
@@ -1843,7 +1843,7 @@
         <v>45729</v>
       </c>
       <c r="B55" t="n">
-        <v>3.281697028642955</v>
+        <v>2.909855358199674</v>
       </c>
       <c r="C55" t="n">
         <v>24</v>
@@ -1852,13 +1852,13 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>1.668676446166348</v>
+        <v>1.473850767826685</v>
       </c>
       <c r="F55" t="n">
-        <v>2.049806415878602</v>
+        <v>1.837586906717794</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.02484010603130193</v>
+        <v>0.1763813126102681</v>
       </c>
       <c r="H55" t="n">
         <v>24</v>
@@ -1869,7 +1869,7 @@
         <v>45730</v>
       </c>
       <c r="B56" t="n">
-        <v>3.013362424314798</v>
+        <v>3.312391191061544</v>
       </c>
       <c r="C56" t="n">
         <v>24</v>
@@ -1878,13 +1878,13 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>1.574245730608833</v>
+        <v>1.719234111411454</v>
       </c>
       <c r="F56" t="n">
-        <v>1.864462773363057</v>
+        <v>2.042807173979347</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.07023522550438832</v>
+        <v>-0.28477346070431</v>
       </c>
       <c r="H56" t="n">
         <v>24</v>
@@ -1895,7 +1895,7 @@
         <v>45731</v>
       </c>
       <c r="B57" t="n">
-        <v>3.13816786233816</v>
+        <v>3.915892022403362</v>
       </c>
       <c r="C57" t="n">
         <v>24</v>
@@ -1904,13 +1904,13 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>1.596635198232756</v>
+        <v>1.97603869464435</v>
       </c>
       <c r="F57" t="n">
-        <v>1.835303065463165</v>
+        <v>2.359548896649658</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.1119584170328165</v>
+        <v>-0.8379383079772669</v>
       </c>
       <c r="H57" t="n">
         <v>24</v>
@@ -1921,7 +1921,7 @@
         <v>45732</v>
       </c>
       <c r="B58" t="n">
-        <v>8.586171438993977</v>
+        <v>9.139268618505632</v>
       </c>
       <c r="C58" t="n">
         <v>24</v>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>3.423087963616849</v>
+        <v>3.546363583537967</v>
       </c>
       <c r="F58" t="n">
-        <v>5.876500230114136</v>
+        <v>6.057910155818184</v>
       </c>
       <c r="G58" t="n">
-        <v>0.6903970084783125</v>
+        <v>0.6709868247342032</v>
       </c>
       <c r="H58" t="n">
         <v>24</v>
@@ -1947,7 +1947,7 @@
         <v>45733</v>
       </c>
       <c r="B59" t="n">
-        <v>3.561750152120358</v>
+        <v>3.205272735537979</v>
       </c>
       <c r="C59" t="n">
         <v>24</v>
@@ -1956,13 +1956,13 @@
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>1.877010951140439</v>
+        <v>1.679673869038568</v>
       </c>
       <c r="F59" t="n">
-        <v>2.434175667284332</v>
+        <v>2.117713314927602</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.661559309270721</v>
+        <v>-0.2576110622612846</v>
       </c>
       <c r="H59" t="n">
         <v>24</v>
@@ -1973,7 +1973,7 @@
         <v>45734</v>
       </c>
       <c r="B60" t="n">
-        <v>2.955744453474777</v>
+        <v>3.037614883287718</v>
       </c>
       <c r="C60" t="n">
         <v>24</v>
@@ -1982,13 +1982,13 @@
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>1.511698754757565</v>
+        <v>1.559708036014727</v>
       </c>
       <c r="F60" t="n">
-        <v>1.797148947074609</v>
+        <v>1.863045975377515</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0195414712422195</v>
+        <v>-0.05367876527573001</v>
       </c>
       <c r="H60" t="n">
         <v>24</v>
@@ -1999,7 +1999,7 @@
         <v>45735</v>
       </c>
       <c r="B61" t="n">
-        <v>3.884528026584269</v>
+        <v>3.886514411960186</v>
       </c>
       <c r="C61" t="n">
         <v>24</v>
@@ -2008,13 +2008,13 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>1.981016114109552</v>
+        <v>1.963874261783249</v>
       </c>
       <c r="F61" t="n">
-        <v>2.329138334530267</v>
+        <v>2.442000326486976</v>
       </c>
       <c r="G61" t="n">
-        <v>0.1213812104288133</v>
+        <v>0.0341685229976898</v>
       </c>
       <c r="H61" t="n">
         <v>24</v>
@@ -2025,7 +2025,7 @@
         <v>45736</v>
       </c>
       <c r="B62" t="n">
-        <v>2.370865649757516</v>
+        <v>2.892898582207241</v>
       </c>
       <c r="C62" t="n">
         <v>24</v>
@@ -2034,13 +2034,13 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>1.202698093110053</v>
+        <v>1.4802992043981</v>
       </c>
       <c r="F62" t="n">
-        <v>1.571840974116042</v>
+        <v>1.904083312955691</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.158000687794452</v>
+        <v>-0.6992743428089119</v>
       </c>
       <c r="H62" t="n">
         <v>24</v>
@@ -2051,7 +2051,7 @@
         <v>45737</v>
       </c>
       <c r="B63" t="n">
-        <v>2.492013872188031</v>
+        <v>2.660990385643506</v>
       </c>
       <c r="C63" t="n">
         <v>24</v>
@@ -2060,13 +2060,13 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>1.277374042330682</v>
+        <v>1.357585881697998</v>
       </c>
       <c r="F63" t="n">
-        <v>1.554754414724472</v>
+        <v>1.665391179786532</v>
       </c>
       <c r="G63" t="n">
-        <v>0.02941322125835988</v>
+        <v>-0.1136360832899099</v>
       </c>
       <c r="H63" t="n">
         <v>24</v>
@@ -2077,7 +2077,7 @@
         <v>45738</v>
       </c>
       <c r="B64" t="n">
-        <v>2.406652376758947</v>
+        <v>2.562696975024729</v>
       </c>
       <c r="C64" t="n">
         <v>24</v>
@@ -2086,13 +2086,13 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>1.207099576088444</v>
+        <v>1.279989703026658</v>
       </c>
       <c r="F64" t="n">
-        <v>1.482869145155338</v>
+        <v>1.651347628385147</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.3482028799302046</v>
+        <v>-0.6719627877136685</v>
       </c>
       <c r="H64" t="n">
         <v>24</v>
@@ -2103,7 +2103,7 @@
         <v>45739</v>
       </c>
       <c r="B65" t="n">
-        <v>2.760383301756662</v>
+        <v>2.884425396560163</v>
       </c>
       <c r="C65" t="n">
         <v>24</v>
@@ -2112,13 +2112,13 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>1.401990638771653</v>
+        <v>1.456572247200361</v>
       </c>
       <c r="F65" t="n">
-        <v>1.696175065984521</v>
+        <v>1.767289508430337</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.1322565613196178</v>
+        <v>-0.229189651015612</v>
       </c>
       <c r="H65" t="n">
         <v>24</v>
@@ -2129,7 +2129,7 @@
         <v>45740</v>
       </c>
       <c r="B66" t="n">
-        <v>1.928776347455486</v>
+        <v>1.996938067914904</v>
       </c>
       <c r="C66" t="n">
         <v>24</v>
@@ -2138,13 +2138,13 @@
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>1.013042502964923</v>
+        <v>1.038296917184516</v>
       </c>
       <c r="F66" t="n">
-        <v>1.248165815928943</v>
+        <v>1.274321143219819</v>
       </c>
       <c r="G66" t="n">
-        <v>0.01603402729724923</v>
+        <v>-0.02563607822083314</v>
       </c>
       <c r="H66" t="n">
         <v>24</v>
@@ -2155,7 +2155,7 @@
         <v>45741</v>
       </c>
       <c r="B67" t="n">
-        <v>3.942257033438611</v>
+        <v>4.022372256822689</v>
       </c>
       <c r="C67" t="n">
         <v>24</v>
@@ -2164,13 +2164,13 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>1.981480811140983</v>
+        <v>2.002248341190968</v>
       </c>
       <c r="F67" t="n">
-        <v>2.491571265538461</v>
+        <v>2.572012721049818</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.2880553243676132</v>
+        <v>-0.372568773776474</v>
       </c>
       <c r="H67" t="n">
         <v>24</v>
@@ -2181,7 +2181,7 @@
         <v>45742</v>
       </c>
       <c r="B68" t="n">
-        <v>3.676244869348114</v>
+        <v>3.709144596927153</v>
       </c>
       <c r="C68" t="n">
         <v>24</v>
@@ -2190,13 +2190,13 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>1.878888887261252</v>
+        <v>1.891080946294281</v>
       </c>
       <c r="F68" t="n">
-        <v>2.206786317557492</v>
+        <v>2.273233144926999</v>
       </c>
       <c r="G68" t="n">
-        <v>-0.1542704983251753</v>
+        <v>-0.2248276728153318</v>
       </c>
       <c r="H68" t="n">
         <v>24</v>
@@ -2207,7 +2207,7 @@
         <v>45743</v>
       </c>
       <c r="B69" t="n">
-        <v>3.527923015510773</v>
+        <v>3.224252899456401</v>
       </c>
       <c r="C69" t="n">
         <v>24</v>
@@ -2216,13 +2216,13 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>1.787823422078666</v>
+        <v>1.623896364492816</v>
       </c>
       <c r="F69" t="n">
-        <v>2.264355390694564</v>
+        <v>2.206711741209834</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.04589478143423187</v>
+        <v>0.006678062960423059</v>
       </c>
       <c r="H69" t="n">
         <v>24</v>
@@ -2233,7 +2233,7 @@
         <v>45744</v>
       </c>
       <c r="B70" t="n">
-        <v>3.335398328980899</v>
+        <v>3.202485588348779</v>
       </c>
       <c r="C70" t="n">
         <v>24</v>
@@ -2242,13 +2242,13 @@
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>1.748804327028207</v>
+        <v>1.678422375841654</v>
       </c>
       <c r="F70" t="n">
-        <v>2.156756888287968</v>
+        <v>2.147420035261745</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.06070526400639809</v>
+        <v>-0.05154130845850258</v>
       </c>
       <c r="H70" t="n">
         <v>24</v>
@@ -2259,7 +2259,7 @@
         <v>45745</v>
       </c>
       <c r="B71" t="n">
-        <v>1.786274899602884</v>
+        <v>2.133824463417255</v>
       </c>
       <c r="C71" t="n">
         <v>24</v>
@@ -2268,13 +2268,13 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>0.9210570276267873</v>
+        <v>1.104770492937209</v>
       </c>
       <c r="F71" t="n">
-        <v>1.260040022177453</v>
+        <v>1.319727445212691</v>
       </c>
       <c r="G71" t="n">
-        <v>0.1494020699238664</v>
+        <v>0.06690870236399593</v>
       </c>
       <c r="H71" t="n">
         <v>24</v>
@@ -2285,7 +2285,7 @@
         <v>45746</v>
       </c>
       <c r="B72" t="n">
-        <v>4.042386218953122</v>
+        <v>4.007488218789903</v>
       </c>
       <c r="C72" t="n">
         <v>24</v>
@@ -2294,13 +2294,13 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>2.132083849068298</v>
+        <v>2.100003743994184</v>
       </c>
       <c r="F72" t="n">
-        <v>2.485278209967671</v>
+        <v>2.559194485953305</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.4126435645411173</v>
+        <v>-0.4979218431265089</v>
       </c>
       <c r="H72" t="n">
         <v>24</v>
@@ -2311,7 +2311,7 @@
         <v>45747</v>
       </c>
       <c r="B73" t="n">
-        <v>2.759459771374704</v>
+        <v>2.664964464290029</v>
       </c>
       <c r="C73" t="n">
         <v>24</v>
@@ -2320,13 +2320,13 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>1.422138655172748</v>
+        <v>1.370372329069434</v>
       </c>
       <c r="F73" t="n">
-        <v>1.812649344389245</v>
+        <v>1.781307796517204</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.3562221467869731</v>
+        <v>-0.309728183278992</v>
       </c>
       <c r="H73" t="n">
         <v>24</v>
@@ -2337,7 +2337,7 @@
         <v>45748</v>
       </c>
       <c r="B74" t="n">
-        <v>5.815438381734548</v>
+        <v>5.615636418332312</v>
       </c>
       <c r="C74" t="n">
         <v>24</v>
@@ -2346,13 +2346,13 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>1.815683043852946</v>
+        <v>1.743140744000077</v>
       </c>
       <c r="F74" t="n">
-        <v>5.34974430481401</v>
+        <v>5.260393179714004</v>
       </c>
       <c r="G74" t="n">
-        <v>0.7242284501806489</v>
+        <v>0.7333633638343073</v>
       </c>
       <c r="H74" t="n">
         <v>24</v>
@@ -2363,7 +2363,7 @@
         <v>45749</v>
       </c>
       <c r="B75" t="n">
-        <v>2.069236746634851</v>
+        <v>1.953639653286101</v>
       </c>
       <c r="C75" t="n">
         <v>24</v>
@@ -2372,13 +2372,13 @@
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>0.6286757567403217</v>
+        <v>0.5945729168509911</v>
       </c>
       <c r="F75" t="n">
-        <v>0.7490283034774539</v>
+        <v>0.7305003669396</v>
       </c>
       <c r="G75" t="n">
-        <v>-0.05623859293592748</v>
+        <v>-0.004630713504164996</v>
       </c>
       <c r="H75" t="n">
         <v>24</v>
@@ -2389,7 +2389,7 @@
         <v>45750</v>
       </c>
       <c r="B76" t="n">
-        <v>2.347196997656127</v>
+        <v>2.264109941306561</v>
       </c>
       <c r="C76" t="n">
         <v>24</v>
@@ -2398,13 +2398,13 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>0.6950285308584565</v>
+        <v>0.6700791666472639</v>
       </c>
       <c r="F76" t="n">
-        <v>0.8180319518736698</v>
+        <v>0.8040282364302181</v>
       </c>
       <c r="G76" t="n">
-        <v>-0.2109550256505202</v>
+        <v>-0.1698497351554855</v>
       </c>
       <c r="H76" t="n">
         <v>24</v>
@@ -2415,7 +2415,7 @@
         <v>45751</v>
       </c>
       <c r="B77" t="n">
-        <v>2.440875470089414</v>
+        <v>2.462307254976038</v>
       </c>
       <c r="C77" t="n">
         <v>24</v>
@@ -2424,13 +2424,13 @@
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>0.7368449653714896</v>
+        <v>0.7432020833430347</v>
       </c>
       <c r="F77" t="n">
-        <v>0.9362830066627418</v>
+        <v>0.9327397706264198</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.2141060098783301</v>
+        <v>-0.2049341585794031</v>
       </c>
       <c r="H77" t="n">
         <v>24</v>
@@ -2441,7 +2441,7 @@
         <v>45752</v>
       </c>
       <c r="B78" t="n">
-        <v>1.98278116712646</v>
+        <v>1.97826896568997</v>
       </c>
       <c r="C78" t="n">
         <v>24</v>
@@ -2450,13 +2450,13 @@
         <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>0.5952689194910229</v>
+        <v>0.5942437499902985</v>
       </c>
       <c r="F78" t="n">
-        <v>0.6735096182580107</v>
+        <v>0.6762719209908521</v>
       </c>
       <c r="G78" t="n">
-        <v>0.121086077956376</v>
+        <v>0.1138618158139579</v>
       </c>
       <c r="H78" t="n">
         <v>24</v>
@@ -2467,7 +2467,7 @@
         <v>45753</v>
       </c>
       <c r="B79" t="n">
-        <v>2.285155645212453</v>
+        <v>2.13204224847294</v>
       </c>
       <c r="C79" t="n">
         <v>24</v>
@@ -2476,13 +2476,13 @@
         <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>0.6879270671047268</v>
+        <v>0.642822916715173</v>
       </c>
       <c r="F79" t="n">
-        <v>0.9185956751034066</v>
+        <v>0.8858431964424693</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.2803226431962456</v>
+        <v>-0.1906506176027454</v>
       </c>
       <c r="H79" t="n">
         <v>24</v>
@@ -2493,7 +2493,7 @@
         <v>45754</v>
       </c>
       <c r="B80" t="n">
-        <v>1.803876078558025</v>
+        <v>1.847343303981641</v>
       </c>
       <c r="C80" t="n">
         <v>24</v>
@@ -2502,13 +2502,13 @@
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>0.5501221649505195</v>
+        <v>0.5626312499902987</v>
       </c>
       <c r="F80" t="n">
-        <v>0.7124532777125258</v>
+        <v>0.7071604703019253</v>
       </c>
       <c r="G80" t="n">
-        <v>0.04349784817442082</v>
+        <v>0.05765674646000951</v>
       </c>
       <c r="H80" t="n">
         <v>24</v>
@@ -2519,7 +2519,7 @@
         <v>45755</v>
       </c>
       <c r="B81" t="n">
-        <v>11.52566410973955</v>
+        <v>11.95362991370904</v>
       </c>
       <c r="C81" t="n">
         <v>24</v>
@@ -2528,13 +2528,13 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>2.602245923370868</v>
+        <v>2.695792555010753</v>
       </c>
       <c r="F81" t="n">
-        <v>5.483106550190415</v>
+        <v>5.699869650314024</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.7052334286384494</v>
+        <v>-0.8427240964157339</v>
       </c>
       <c r="H81" t="n">
         <v>24</v>
@@ -2545,7 +2545,7 @@
         <v>45756</v>
       </c>
       <c r="B82" t="n">
-        <v>2.061572400413219</v>
+        <v>2.104199379422504</v>
       </c>
       <c r="C82" t="n">
         <v>24</v>
@@ -2554,13 +2554,13 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0.6240195204451684</v>
+        <v>0.6375458333333338</v>
       </c>
       <c r="F82" t="n">
-        <v>0.7601267001039466</v>
+        <v>0.7715824436051016</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.07842275644340702</v>
+        <v>-0.1111731598654497</v>
       </c>
       <c r="H82" t="n">
         <v>24</v>
@@ -2571,7 +2571,7 @@
         <v>45757</v>
       </c>
       <c r="B83" t="n">
-        <v>2.548487399867214</v>
+        <v>2.530044490066619</v>
       </c>
       <c r="C83" t="n">
         <v>23</v>
@@ -2580,13 +2580,13 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>0.7751804152794513</v>
+        <v>0.7699130434580151</v>
       </c>
       <c r="F83" t="n">
-        <v>0.8859565978012492</v>
+        <v>0.9016433197481132</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.1391897084943574</v>
+        <v>-0.1798877662686273</v>
       </c>
       <c r="H83" t="n">
         <v>23</v>
